--- a/data/QMthermoScan_C_wB97Mp2_def2QZVPP.xlsx
+++ b/data/QMthermoScan_C_wB97Mp2_def2QZVPP.xlsx
@@ -466,42 +466,42 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>zpe/J</t>
+          <t>zpe/(J/mol)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>U_corr/J</t>
+          <t>U_corr/(J/mol)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>H_corr/J</t>
+          <t>H_corr/(J/mol)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>G_corr/J</t>
+          <t>G_corr/(J/mol)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>ee/J</t>
+          <t>ee/(J/mol)</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>U/J</t>
+          <t>U/(J/mol)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>H/J</t>
+          <t>H/(J/mol)</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>G/J</t>
+          <t>G/(J/mol)</t>
         </is>
       </c>
     </row>
